--- a/docs/RoboCore_V2_quote_request_2_robots.xlsx
+++ b/docs/RoboCore_V2_quote_request_2_robots.xlsx
@@ -366,10 +366,10 @@
     <from>
       <col>1</col>
       <colOff>66675</colOff>
-      <row>14</row>
-      <rowOff>114300</rowOff>
+      <row>15</row>
+      <rowOff>38100</rowOff>
     </from>
-    <ext cx="1143000" cy="704850"/>
+    <ext cx="1143000" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -392,9 +392,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>16</row>
-      <rowOff>38100</rowOff>
+      <rowOff>85725</rowOff>
     </from>
-    <ext cx="1143000" cy="857250"/>
+    <ext cx="1143000" cy="762000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -415,11 +415,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>66675</colOff>
+      <colOff>95250</colOff>
       <row>17</row>
-      <rowOff>85725</rowOff>
+      <rowOff>38100</rowOff>
     </from>
-    <ext cx="1143000" cy="762000"/>
+    <ext cx="1085850" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -440,11 +440,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>161925</colOff>
-      <row>18</row>
-      <rowOff>161925</rowOff>
+      <colOff>76200</colOff>
+      <row>19</row>
+      <rowOff>38100</rowOff>
     </from>
-    <ext cx="952500" cy="609600"/>
+    <ext cx="1114425" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -465,11 +465,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>95250</colOff>
-      <row>19</row>
+      <colOff>66675</colOff>
+      <row>21</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="1085850" cy="857250"/>
+    <ext cx="1143000" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -491,7 +491,7 @@
     <from>
       <col>1</col>
       <colOff>66675</colOff>
-      <row>20</row>
+      <row>22</row>
       <rowOff>38100</rowOff>
     </from>
     <ext cx="1143000" cy="857250"/>
@@ -515,11 +515,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>76200</colOff>
-      <row>22</row>
+      <colOff>133350</colOff>
+      <row>23</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="1114425" cy="857250"/>
+    <ext cx="1000125" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -540,11 +540,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>314325</colOff>
-      <row>23</row>
+      <colOff>66675</colOff>
+      <row>24</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="647700" cy="857250"/>
+    <ext cx="1143000" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -567,9 +567,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>25</row>
-      <rowOff>38100</rowOff>
+      <rowOff>85725</rowOff>
     </from>
-    <ext cx="1143000" cy="857250"/>
+    <ext cx="1143000" cy="762000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -590,11 +590,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>66675</colOff>
+      <colOff>133350</colOff>
       <row>26</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="1143000" cy="857250"/>
+    <ext cx="1000125" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -640,11 +640,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>66675</colOff>
+      <colOff>133350</colOff>
       <row>28</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="1143000" cy="857250"/>
+    <ext cx="1000125" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -665,11 +665,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>66675</colOff>
+      <colOff>209550</colOff>
       <row>29</row>
-      <rowOff>85725</rowOff>
+      <rowOff>38100</rowOff>
     </from>
-    <ext cx="1143000" cy="762000"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -690,11 +690,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>133350</colOff>
+      <colOff>66675</colOff>
       <row>30</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="1000125" cy="857250"/>
+    <ext cx="1143000" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -715,11 +715,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>133350</colOff>
+      <colOff>95250</colOff>
       <row>31</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="1000125" cy="857250"/>
+    <ext cx="1085850" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -740,11 +740,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>133350</colOff>
+      <colOff>371475</colOff>
       <row>32</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="1000125" cy="857250"/>
+    <ext cx="533400" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -765,11 +765,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>209550</colOff>
+      <colOff>104775</colOff>
       <row>33</row>
       <rowOff>38100</rowOff>
     </from>
-    <ext cx="857250" cy="857250"/>
+    <ext cx="1066800" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -791,10 +791,10 @@
     <from>
       <col>1</col>
       <colOff>66675</colOff>
-      <row>34</row>
-      <rowOff>38100</rowOff>
+      <row>35</row>
+      <rowOff>142875</rowOff>
     </from>
-    <ext cx="1143000" cy="857250"/>
+    <ext cx="1143000" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -815,11 +815,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>95250</colOff>
-      <row>35</row>
-      <rowOff>38100</rowOff>
+      <colOff>66675</colOff>
+      <row>36</row>
+      <rowOff>142875</rowOff>
     </from>
-    <ext cx="1085850" cy="857250"/>
+    <ext cx="1143000" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -840,11 +840,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>371475</colOff>
-      <row>36</row>
-      <rowOff>38100</rowOff>
+      <colOff>66675</colOff>
+      <row>37</row>
+      <rowOff>142875</rowOff>
     </from>
-    <ext cx="533400" cy="857250"/>
+    <ext cx="1143000" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -865,11 +865,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>104775</colOff>
-      <row>37</row>
-      <rowOff>38100</rowOff>
+      <colOff>66675</colOff>
+      <row>38</row>
+      <rowOff>142875</rowOff>
     </from>
-    <ext cx="1066800" cy="857250"/>
+    <ext cx="1143000" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -877,106 +877,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>39</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <ext cx="1143000" cy="647700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>40</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <ext cx="1143000" cy="647700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>41</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <ext cx="1143000" cy="647700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>42</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <ext cx="1143000" cy="647700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1279,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1596,11 +1496,11 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>MG90S, with horns and screws</t>
+          <t>MG90S, with horns and screws (one for the shoulder, one for the gripper of each robot)</t>
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1624,61 +1524,65 @@
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="14" t="n"/>
     </row>
-    <row r="15" ht="74" customHeight="1">
-      <c r="A15" s="10" t="n">
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Battery and power</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="74" customHeight="1">
+      <c r="A16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Micro servo</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>SG90 (9 g), with horns and screws</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>18650 Li-ion cell</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Genuine branded cell (Samsung, LG, Molicel, EVE or similar), about 3000 mAh, 65 mm long, unprotected</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>pcs</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="14" t="n"/>
-      <c r="J15" s="14" t="n"/>
-      <c r="K15" s="15" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="14" t="n"/>
-      <c r="N15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Battery and power</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>All cells the same model and batch. Protected cells (about 70 mm long) don't fit. Please state brand and model.</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
     </row>
     <row r="17" ht="74" customHeight="1">
       <c r="A17" s="10" t="n">
@@ -1687,16 +1591,16 @@
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18650 Li-ion cell</t>
+          <t>Battery holder, 3 x 18650 *</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Genuine branded cell (Samsung, LG, Molicel, EVE or similar), about 3000 mAh, 65 mm long, unprotected</t>
+          <t>3-cell 18650 holder with wire leads, about 61.6 x 78.4 mm</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1710,7 +1614,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>All cells the same model and batch. Protected cells (about 70 mm long) don't fit. Please state brand and model.</t>
+          <t>We need the cells in PARALLEL (3.7 V out). Please state whether the holder is wired in series or parallel.</t>
         </is>
       </c>
       <c r="I17" s="14" t="n"/>
@@ -1727,16 +1631,16 @@
       <c r="B18" s="11" t="n"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Battery holder, 3 x 18650 *</t>
+          <t>XT30 battery lead, female *</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>3-cell 18650 holder with wire leads, about 61.6 x 78.4 mm</t>
+          <t>AMASS XT30U-F (female) with 10-15 cm of 16 AWG silicone wire</t>
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1745,12 +1649,12 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>We need the cells in PARALLEL (3.7 V out). Please state whether the holder is wired in series or parallel.</t>
+          <t>Female plug, which mates with an XT30 male (XT30UPB-M on our board).</t>
         </is>
       </c>
       <c r="I18" s="14" t="n"/>
@@ -1760,63 +1664,43 @@
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
     </row>
-    <row r="19" ht="74" customHeight="1">
-      <c r="A19" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>1S Li-ion protection board *</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>1S (3.7 V) 18650 protection board, DW01 + 8205A type, rated 5 A or more</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>5-10</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>Protection only (no charger needed).</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="14" t="n"/>
-      <c r="N19" s="14" t="n"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Cables</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
     </row>
     <row r="20" ht="74" customHeight="1">
       <c r="A20" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" s="11" t="n"/>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>XT30 battery lead, female *</t>
+          <t>Dupont jumper wires, female-female</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>AMASS XT30U-F (female) with 10-15 cm of 16 AWG silicone wire</t>
+          <t>2.54 mm, female-female, 20 cm</t>
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1825,14 +1709,10 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>Female plug, which mates with an XT30 male (XT30UPB-M on our board).</t>
-        </is>
-      </c>
+          <t>40-wire strip</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="14" t="n"/>
       <c r="K20" s="15" t="n"/>
@@ -1840,79 +1720,79 @@
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="14" t="n"/>
     </row>
-    <row r="21" ht="74" customHeight="1">
-      <c r="A21" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Heat-shrink tubing assortment</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Assorted sizes, small box</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="14" t="n"/>
-      <c r="J21" s="14" t="n"/>
-      <c r="K21" s="15" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
-      <c r="N21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Screws, inserts and small hardware</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="74" customHeight="1">
+      <c r="A22" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Heat-set insert, M2 (brass) *</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>M2 brass heat-set insert for Ø3.2 mm holes, e.g. M2 x 3 mm long, 3.2 mm OD</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>50-100</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
     </row>
     <row r="23" ht="74" customHeight="1">
       <c r="A23" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Dupont jumper wires, female-female</t>
+          <t>Heat-set insert, M3 short (brass)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>2.54 mm, female-female, 20 cm</t>
+          <t>M3 brass heat-set insert for Ø4.0 mm holes, e.g. M3 x 4 mm long, 4.0 mm OD</t>
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1921,7 +1801,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>40-wire strip</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr"/>
@@ -1934,21 +1814,21 @@
     </row>
     <row r="24" ht="74" customHeight="1">
       <c r="A24" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>USB-C cable</t>
+          <t>Machine screw M2 x 6, pan head</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>USB-A to USB-C or USB-C to USB-C, data + charging</t>
+          <t>M2 x 6 mm pan head machine screw, steel</t>
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1957,14 +1837,10 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>Must carry data (not charge-only).</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="14" t="n"/>
       <c r="J24" s="14" t="n"/>
       <c r="K24" s="15" t="n"/>
@@ -1972,25 +1848,41 @@
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Screws, inserts and small hardware</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
+    <row r="25" ht="74" customHeight="1">
+      <c r="A25" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Self-tapping screw M2 x 6, pan head</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>M2 x 6 mm pan head self-tapping screw (for plastic)</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="15" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="14" t="n"/>
     </row>
     <row r="26" ht="74" customHeight="1">
       <c r="A26" s="10" t="n">
@@ -1999,16 +1891,16 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Heat-set insert, M2 (brass) *</t>
+          <t>Flat washer M2</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>M2 brass heat-set insert for Ø3.2 mm holes, e.g. M2 x 3 mm long, 3.2 mm OD</t>
+          <t>M2 flat washer, steel</t>
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -2017,7 +1909,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr"/>
@@ -2035,16 +1927,16 @@
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Heat-set insert, M3 short (brass)</t>
+          <t>Machine screw M2 x 8, pan head</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>M3 brass heat-set insert for Ø4.0 mm holes, e.g. M3 x 4 mm long, 4.0 mm OD</t>
+          <t>M2 x 8 mm pan head machine screw, steel</t>
         </is>
       </c>
       <c r="E27" s="13" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -2053,7 +1945,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr"/>
@@ -2071,16 +1963,16 @@
       <c r="B28" s="11" t="n"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Machine screw M2 x 6, pan head</t>
+          <t>Screw M2 x 5, pan head</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>M2 x 6 mm pan head machine screw, steel</t>
+          <t>M2 x 5 mm pan head screw, steel</t>
         </is>
       </c>
       <c r="E28" s="13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -2107,16 +1999,16 @@
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Self-tapping screw M2 x 6, pan head</t>
+          <t>Screw M2 x 4, pan head</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>M2 x 6 mm pan head self-tapping screw (for plastic)</t>
+          <t>M2 x 4 mm pan head screw, steel</t>
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -2143,12 +2035,12 @@
       <c r="B30" s="11" t="n"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Flat washer M2</t>
+          <t>Socket head cap screw M3 x 10</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>M2 flat washer, steel</t>
+          <t>M3 x 10 mm hex socket head cap screw, steel</t>
         </is>
       </c>
       <c r="E30" s="13" t="n">
@@ -2161,7 +2053,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr"/>
@@ -2179,12 +2071,12 @@
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Machine screw M2 x 8, pan head</t>
+          <t>Self-tapping screw M3 x 8, pan head</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>M2 x 8 mm pan head machine screw, steel</t>
+          <t>M3 x 8 mm pan head self-tapping screw (for plastic)</t>
         </is>
       </c>
       <c r="E31" s="13" t="n">
@@ -2215,16 +2107,16 @@
       <c r="B32" s="11" t="n"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Screw M2 x 5, pan head</t>
+          <t>Thumb screw M3 x 8, knurled head *</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>M2 x 5 mm pan head screw, steel</t>
+          <t>M3 x 8 mm thumb screw with knurled head</t>
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -2233,7 +2125,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr"/>
@@ -2251,16 +2143,16 @@
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Screw M2 x 4, pan head</t>
+          <t>Hex nut M8</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>M2 x 4 mm pan head screw, steel</t>
+          <t>M8 hex nut, plain steel (about 5 g each)</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -2269,7 +2161,7 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr"/>
@@ -2287,12 +2179,12 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Socket head cap screw M3 x 10</t>
+          <t>Steel ball ½" (12.7 mm)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>M3 x 10 mm hex socket head cap screw, steel</t>
+          <t>12.7 mm (½") steel bearing ball</t>
         </is>
       </c>
       <c r="E34" s="13" t="n">
@@ -2305,10 +2197,14 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>12.7 mm glass marbles are also acceptable.</t>
+        </is>
+      </c>
       <c r="I34" s="14" t="n"/>
       <c r="J34" s="14" t="n"/>
       <c r="K34" s="15" t="n"/>
@@ -2316,71 +2212,59 @@
       <c r="M34" s="14" t="n"/>
       <c r="N34" s="14" t="n"/>
     </row>
-    <row r="35" ht="74" customHeight="1">
-      <c r="A35" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Self-tapping screw M3 x 8, pan head</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>M3 x 8 mm pan head self-tapping screw (for plastic)</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr"/>
-      <c r="I35" s="14" t="n"/>
-      <c r="J35" s="14" t="n"/>
-      <c r="K35" s="15" t="n"/>
-      <c r="L35" s="14" t="n"/>
-      <c r="M35" s="14" t="n"/>
-      <c r="N35" s="14" t="n"/>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>3D-printing filament</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
     </row>
     <row r="36" ht="74" customHeight="1">
       <c r="A36" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="11" t="n"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Thumb screw M3 x 8, knurled head *</t>
+          <t>PETG filament, yellow</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>M3 x 8 mm thumb screw with knurled head</t>
+          <t>PETG 3D-printer filament, 1.75 mm, yellow</t>
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>spool</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr"/>
+          <t>1 kg spool</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>About 370 g needed.</t>
+        </is>
+      </c>
       <c r="I36" s="14" t="n"/>
       <c r="J36" s="14" t="n"/>
       <c r="K36" s="15" t="n"/>
@@ -2390,33 +2274,37 @@
     </row>
     <row r="37" ht="74" customHeight="1">
       <c r="A37" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Hex nut M8</t>
+          <t>PETG filament, black</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>M8 hex nut, plain steel (about 5 g each)</t>
+          <t>PETG 3D-printer filament, 1.75 mm, black</t>
         </is>
       </c>
       <c r="E37" s="13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>spool</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr"/>
+          <t>1 kg spool</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>About 41 g needed.</t>
+        </is>
+      </c>
       <c r="I37" s="14" t="n"/>
       <c r="J37" s="14" t="n"/>
       <c r="K37" s="15" t="n"/>
@@ -2426,35 +2314,35 @@
     </row>
     <row r="38" ht="74" customHeight="1">
       <c r="A38" s="10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Steel ball ½" (12.7 mm)</t>
+          <t>PETG filament, dark teal</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>12.7 mm (½") steel bearing ball</t>
+          <t>PETG 3D-printer filament, 1.75 mm, dark teal</t>
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>spool</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1 kg spool</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>12.7 mm glass marbles are also acceptable.</t>
+          <t>About 36 g needed.</t>
         </is>
       </c>
       <c r="I38" s="14" t="n"/>
@@ -2464,218 +2352,78 @@
       <c r="M38" s="14" t="n"/>
       <c r="N38" s="14" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>3D-printing filament</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="9" t="n"/>
-      <c r="N39" s="9" t="n"/>
-    </row>
-    <row r="40" ht="74" customHeight="1">
-      <c r="A40" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>PETG filament, yellow</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>PETG 3D-printer filament, 1.75 mm, yellow</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="n">
+    <row r="39" ht="74" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>TPU filament, black</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>TPU 95A flexible filament, 1.75 mm, black</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>spool</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>1 kg spool</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>About 370 g needed.</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="n"/>
-      <c r="J40" s="14" t="n"/>
-      <c r="K40" s="15" t="n"/>
-      <c r="L40" s="14" t="n"/>
-      <c r="M40" s="14" t="n"/>
-      <c r="N40" s="14" t="n"/>
-    </row>
-    <row r="41" ht="74" customHeight="1">
-      <c r="A41" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>PETG filament, black</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>PETG 3D-printer filament, 1.75 mm, black</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>spool</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>1 kg spool</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>About 41 g needed.</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="n"/>
-      <c r="J41" s="14" t="n"/>
-      <c r="K41" s="15" t="n"/>
-      <c r="L41" s="14" t="n"/>
-      <c r="M41" s="14" t="n"/>
-      <c r="N41" s="14" t="n"/>
-    </row>
-    <row r="42" ht="74" customHeight="1">
-      <c r="A42" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>PETG filament, dark teal</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>PETG 3D-printer filament, 1.75 mm, dark teal</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>spool</t>
-        </is>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>1 kg spool</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="inlineStr">
-        <is>
-          <t>About 36 g needed.</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="n"/>
-      <c r="J42" s="14" t="n"/>
-      <c r="K42" s="15" t="n"/>
-      <c r="L42" s="14" t="n"/>
-      <c r="M42" s="14" t="n"/>
-      <c r="N42" s="14" t="n"/>
-    </row>
-    <row r="43" ht="74" customHeight="1">
-      <c r="A43" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>TPU filament, black</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>TPU 95A flexible filament, 1.75 mm, black</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>spool</t>
-        </is>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>250 g-1 kg spool</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>About 21 g needed. A small spool is enough.</t>
         </is>
       </c>
-      <c r="I43" s="14" t="n"/>
-      <c r="J43" s="14" t="n"/>
-      <c r="K43" s="15" t="n"/>
-      <c r="L43" s="14" t="n"/>
-      <c r="M43" s="14" t="n"/>
-      <c r="N43" s="14" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="15" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="14" t="n"/>
+    </row>
+    <row r="41">
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>Total for the items quoted</t>
+        </is>
+      </c>
+      <c r="K41" s="17">
+        <f>SUM(K10:K39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>Shipping to Zambia (USD)</t>
+        </is>
+      </c>
+      <c r="K42" s="18" t="n"/>
+    </row>
+    <row r="43">
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>Grand total (USD)</t>
+        </is>
+      </c>
+      <c r="K43" s="17">
+        <f>K41+K42</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>Total for the items quoted</t>
-        </is>
-      </c>
-      <c r="K45" s="17">
-        <f>SUM(K10:K43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>Shipping to Zambia (USD)</t>
-        </is>
-      </c>
-      <c r="K46" s="18" t="n"/>
-    </row>
-    <row r="47">
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>Grand total (USD)</t>
-        </is>
-      </c>
-      <c r="K47" s="17">
-        <f>K45+K46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Prices in USD. Please state any minimum order, payment terms and the shipping method.</t>
         </is>
@@ -2689,7 +2437,7 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I11 I12 I13 I14 I15 I17 I18 I19 I20 I21 I23 I24 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I40 I41 I42 I43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I11 I12 I13 I14 I16 I17 I18 I20 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N,Partly"</formula1>
     </dataValidation>
   </dataValidations>
